--- a/mock-data/out/지역NW운용본부_20260828.xlsx
+++ b/mock-data/out/지역NW운용본부_20260828.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="서부" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보안통제" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TACS원본추출" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74144,4 +74145,9544 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D433"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>HostID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>장비명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>등록일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HOST00001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KTBCP001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>10.25.1.2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HOST00003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KTCLD001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10.20.1.4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HOST00005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KTDB002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10.21.1.6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HOST00006</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KTGE001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.23.1.7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HOST00007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KTCLD002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10.20.1.8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HOST00008</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KTBCP003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10.25.1.9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HOST00009</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KTBCP004</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10.25.1.10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HOST00010</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KTGE002</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10.23.1.11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HOST00011</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KTIPTV001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10.22.1.12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HOST00012</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KTBCP005</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10.25.1.13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HOST00013</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KTGE003</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.23.1.14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HOST00014</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KTGE004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10.23.1.15</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HOST00015</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KTAI001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.24.1.16</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HOST00016</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KTAI002</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.24.1.17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HOST00017</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KTIPTV002</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10.22.1.18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HOST00019</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KTBCP007</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10.25.1.20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HOST00020</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KTIPTV003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10.22.1.21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024-01-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HOST00021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KTDB003</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10.21.1.163</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HOST00022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KTCLD003</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10.20.1.23</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HOST00023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KTIPTV004</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10.22.1.24</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HOST00024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KTAI003</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10.24.1.25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HOST00025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KTAI004</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10.24.1.26</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HOST00026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KTIP-TV005</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10.22.1.27</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HOST00027</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KTBCP008</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10.25.1.28</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HOST00028</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KTAI005</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10.24.1.29</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HOST00029</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KTAI006</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10.24.1.30</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HOST00030</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KTCLD004</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10.20.1.31</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HOST00031</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KTGE005</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10.23.1.32</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HOST00032</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KTIPTV006</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10.22.1.33</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HOST00033</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>KTAI007</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10.24.1.160</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HOST00034</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KTBCP009</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10.25.1.35</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HOST00035</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KTCLD005</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10.20.1.36</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HOST00036</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KTGE006</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10.23.1.37</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HOST00037</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KTDB004</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10.21.1.38</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HOST00038</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KTIPTV007</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10.22.1.39</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HOST00039</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KTDB005</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10.21.1.40</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HOST00040</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KTGE007</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10.23.1.41</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HOST00041</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KTGE008</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10.23.1.42</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>HOST00042</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KTGE009</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10.23.1.43</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HOST00043</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KTIPTV008</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10.22.1.44</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>HOST00044</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>KTGE010</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10.23.1.45</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HOST00045</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KTCLD006</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10.20.1.46</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>HOST00046</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KTGE011</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10.23.1.47</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HOST00047</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KTAI008</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10.24.1.48</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HOST00049</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KTAI009</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>10.24.1.50</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HOST00050</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>KTBCP010</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>10.25.1.51</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HOST00051</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KTBCP011</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10.25.1.52</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HOST00052</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>KTBCP012</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>10.25.1.53</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>HOST00054</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>KTIPTV009</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10.22.1.55</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>HOST00056</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KTBCP013</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10.25.1.57</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>HOST00057</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>KTAI010</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10.24.1.58</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>HOST00058</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KTCLD007</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10.20.1.59</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>HOST00060</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KTBCP014</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>10.25.1.61</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>HOST00061</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KTBCP015</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>10.25.1.62</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>HOST00062</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KTAI011</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10.24.1.63</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HOST00063</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KTDB008</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>10.21.1.64</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HOST00065</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KTBCP017</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>10.25.1.66</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HOST00066</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KTIPTV011</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10.22.1.67</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HOST00067</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KTAI012</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10.24.1.68</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>HOST00068</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KTCLD008</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10.20.1.69</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>HOST00069</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KTGE013</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>10.23.1.70</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>HOST00070</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KTDB009</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10.21.1.71</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>HOST00071</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KTGE014</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>10.23.1.72</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HOST00073</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KTGE015</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>10.23.1.74</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HOST00074</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KTIPTV012</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10.22.1.75</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HOST00076</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KTIP-TV013</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10.22.1.77</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HOST00077</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KTGE017</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>10.23.1.78</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HOST00078</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KTBCP018</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10.25.1.79</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HOST00079</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KT-AI014</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10.24.1.80</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HOST00080</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KTDB010</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10.21.1.137</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HOST00081</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KTDB011</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>10.21.1.82</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HOST00082</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KTGE018</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>10.23.1.83</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HOST00084</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KTIPTV014</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10.22.1.85</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>HOST00085</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KTIPTV015</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>10.22.1.86</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>HOST00086</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KTAI015</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>10.24.1.87</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>HOST00087</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KTDB012</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>10.21.1.88</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HOST00088</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>KTCLD009</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10.20.1.89</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>HOST00089</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KTGE020</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>10.23.1.90</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>HOST00090</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>KTIPTV016</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>10.22.1.91</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>HOST00091</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>KTBCP019</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>10.25.1.92</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HOST00092</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>KTCLD010</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>10.20.1.93</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>HOST00093</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>KTIPTV017</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>10.22.1.53</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>HOST00094</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KTB-CP020</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>10.25.1.95</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>HOST00095</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KTIPTV018</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>10.22.1.96</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HOST00096</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KTDB013</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>10.21.1.97</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HOST00097</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KTDB014</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>10.21.1.98</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>HOST00098</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KTBCP021</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>10.25.1.99</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>HOST00099</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KTDB015</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>10.21.1.100</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HOST00100</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KTCLD011</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>10.20.1.101</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HOST00101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KTAI016</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>10.24.1.102</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>HOST00102</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KTAI017</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>10.24.1.103</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>HOST00103</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KTAI018</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>10.24.1.104</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>HOST00104</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KTAI019</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>10.24.1.105</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HOST00106</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KTBCP022</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>10.25.1.107</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>HOST00107</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>KTBCP023</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>10.25.1.108</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>HOST00108</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KTGE021</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>10.23.1.109</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>HOST00109</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KTAI021</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>10.24.1.110</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>HOST00110</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>KTGE022</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>10.23.1.111</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>HOST00111</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>KTBCP024</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>10.25.1.112</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>HOST00112</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KTIPTV019</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>10.22.1.113</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>HOST00113</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KTIPTV020</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>10.22.1.114</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>HOST00114</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KTBCP025</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>10.25.1.115</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HOST00115</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>KTDB016</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>10.21.1.116</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HOST00116</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>KTBCP026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>10.25.1.117</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>HOST00117</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KT-GE023</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>10.23.1.118</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>HOST00118</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KTGE024</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>10.23.1.119</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>HOST00120</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KTAI022</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>10.24.1.121</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>HOST00121</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>KTGE026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>10.23.1.122</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>HOST00122</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KTIPTV021</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>10.22.1.123</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>HOST00123</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KTGE027</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>10.23.1.124</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>HOST00125</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>KTGE028</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>10.23.1.126</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>HOST00126</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>KTGE029</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>10.23.1.127</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>HOST00127</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>KTAI023</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>10.24.1.37</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>HOST00128</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KTAI024</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>10.24.1.159</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>HOST00129</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KTBCP028</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>10.25.1.130</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>HOST00131</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>KTBCP029</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>10.25.1.152</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HOST00132</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>KTGE030</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>10.23.1.133</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>HOST00135</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>KTCLD013</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>10.20.1.136</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>HOST00136</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>KTIP-TV023</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>10.22.1.137</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>HOST00137</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KTCLD014</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10.20.1.138</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>HOST00138</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KTIPTV024</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>10.22.1.139</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>HOST00139</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>KTIPTV025</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10.22.1.140</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>HOST00140</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>KTAI025</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>10.24.1.141</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>HOST00141</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>KTCLD015</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>10.20.1.142</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>HOST00142</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>KTGE031</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10.23.1.143</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>HOST00143</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>KTCLD016</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>10.20.1.144</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>HOST00144</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>KTCLD017</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>10.20.1.145</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>HOST00145</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>KTAI026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10.24.1.201</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HOST00146</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>KTAI027</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>10.24.1.147</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HOST00147</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>KTDB017</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10.21.1.148</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>HOST00149</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>KTCLD018</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10.20.1.150</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>HOST00150</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>KTIPTV026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>10.22.1.151</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>HOST00151</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>KTDB018</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>10.21.1.152</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>HOST00152</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>KTBCP031</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10.25.1.153</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>HOST00153</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>KTIPTV027</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>10.22.1.154</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>HOST00154</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>KTIPTV028</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>10.22.1.155</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>HOST00155</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>KTCLD019</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>10.20.1.156</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HOST00156</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>KTIPTV029</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>10.22.1.157</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HOST00157</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>KTCLD020</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>10.20.1.158</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>HOST00158</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>KTCLD021</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>10.20.1.159</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>HOST00159</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>KTDB019</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>10.21.1.160</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>HOST00160</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>KTAI028</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>10.24.1.161</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>HOST00161</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KTBCP032</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>10.25.1.162</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>HOST00162</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>KTCLD022</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>10.20.1.163</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>HOST00163</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>KTAI029</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>10.24.1.245</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>HOST00164</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>KTAI030</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>10.24.1.165</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>HOST00166</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>KTIPTV031</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>10.22.1.167</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>HOST00167</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>KTBCP033</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>10.25.1.168</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>HOST00168</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>KTGE033</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>10.23.1.169</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>HOST00169</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>KTDB020</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10.21.1.170</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>HOST00170</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KTDB021</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>10.21.1.171</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HOST00171</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KTGE034</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>10.23.1.172</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>HOST00172</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KTCLD023</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>10.20.1.173</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>HOST00173</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KTGE035</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>10.23.1.174</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>HOST00174</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>KTB-CP034</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>10.25.1.175</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>HOST00176</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>KTDB022</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>10.21.1.63</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>HOST00178</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KTIPTV033</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>10.22.1.179</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HOST00179</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>KTBCP035</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>10.25.1.180</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>HOST00180</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>KTCLD024</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>10.20.1.181</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>HOST00181</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>KTGE036</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>10.23.1.182</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>HOST00182</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>KTCLD025</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>10.20.1.183</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>HOST00183</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>KTBCP036</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>10.25.1.184</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>HOST00184</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>KTCLD026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>10.20.1.185</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>HOST00185</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>KTIP-TV034</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>10.22.1.186</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>HOST00186</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>KTIPTV035</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>10.22.1.187</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>HOST00187</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>KTBCP037</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>10.25.1.188</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>HOST00188</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>KTGE037</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>10.23.1.189</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>HOST00189</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>KTDB023</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>10.21.1.190</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>HOST00190</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>KTGE038</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>10.23.1.191</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>HOST00191</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>KTCLD027</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>10.20.1.192</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>HOST00192</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>KTGE039</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>10.23.1.193</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>HOST00193</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>KTCLD028</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>10.20.1.194</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>HOST00194</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>KTDB024</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>10.21.1.195</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>HOST00195</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>KTCLD029</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>10.20.1.196</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>HOST00196</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>KTDB025</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>10.21.1.197</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>HOST00197</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>KTBCP038</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>10.25.1.198</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>HOST00198</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>KT-DB026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>10.21.1.199</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>HOST00199</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>KTCLD030</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>10.20.1.200</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>HOST00200</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>KTDB027</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>10.21.1.201</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>HOST00201</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>KTGE040</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>10.23.1.202</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>HOST00202</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>KTDB028</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>10.21.1.155</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>HOST00203</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>KTDB029</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>10.21.1.204</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>HOST00204</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>KTAI032</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>10.24.1.205</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>HOST00205</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>KTIPTV036</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>10.22.1.206</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>HOST00206</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>KTBCP039</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>10.25.1.207</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>HOST00207</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>KTIPTV037</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>10.22.1.208</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>HOST00208</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>KTIPTV038</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>10.22.1.209</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>HOST00210</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>KTBCP041</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>10.25.1.211</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>HOST00211</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>KTCLD031</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>10.20.1.212</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>HOST00213</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>KTBCP042</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>10.25.1.214</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>HOST00214</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>KTBCP043</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>10.25.1.215</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>HOST00215</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>KTCLD033</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>10.20.1.216</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>HOST00216</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>KTAI033</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>10.24.1.217</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>HOST00217</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>KTDB030</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>10.21.1.218</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>HOST00218</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>KTDB031</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>10.21.1.219</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>HOST00219</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>KTDB032</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>10.21.1.220</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>HOST00220</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>KTBCP044</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>10.25.1.221</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>HOST00221</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>KTIPTV039</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>10.22.1.222</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>HOST00222</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>KTIPTV040</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>10.22.1.223</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>HOST00223</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>KTGE041</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>10.23.1.224</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>HOST00224</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>KTBCP045</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>10.25.1.225</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>HOST00225</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>KTAI034</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>10.24.1.226</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>HOST00226</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>KTC-LD034</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>10.20.1.227</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>HOST00227</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>KTCLD035</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>10.20.1.228</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>HOST00228</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>KTBCP046</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>10.25.1.229</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>HOST00229</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>KTBCP047</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>10.25.1.230</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>HOST00230</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>KTBCP048</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>10.25.1.231</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>HOST00232</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>KTGE042</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>10.23.1.233</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>HOST00233</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>KTCLD036</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>10.20.1.234</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>HOST00234</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>KTAI035</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>10.24.1.235</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>HOST00235</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>KTGE043</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>10.23.1.236</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>HOST00236</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>KTBCP049</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>10.25.1.237</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>HOST00238</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>KTAI036</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>10.24.1.239</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>HOST00239</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>KTBCP050</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>10.25.1.240</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>HOST00240</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>KTGE044</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>10.23.1.241</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>HOST00241</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>KT-AI037</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>10.24.1.242</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>HOST00242</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>KTCLD037</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>10.20.1.243</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>HOST00243</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>KTIPTV042</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>10.22.1.244</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>HOST00245</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>KTDB034</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>10.21.1.246</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>HOST00246</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>KTAI038</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>10.24.1.247</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>HOST00247</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>KTGE046</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>10.23.1.248</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>HOST00248</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>KTAI039</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>10.24.1.249</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>HOST00249</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>KTCLD038</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>10.20.1.139</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>HOST00250</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>KTIPTV043</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>10.22.1.251</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>HOST00252</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>KTIPTV044</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>10.22.1.253</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>HOST00253</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>KTBCP051</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>10.25.1.254</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>HOST00255</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>KTCLD039</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>10.20.2.2</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>HOST00256</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>KTGE047</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>10.23.2.3</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>HOST00257</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>KTIPTV046</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>10.22.2.4</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2024-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>HOST00258</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>KTCLD040</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>10.20.2.5</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>HOST00259</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>KTDB035</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>10.21.2.124</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>HOST00260</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>KTGE048</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>10.23.2.171</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>HOST00261</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>KTDB036</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>10.21.2.8</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>HOST00263</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>KTGE049</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>10.23.2.10</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>HOST00264</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>KTDB038</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>10.21.2.11</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>HOST00265</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>KTBCP052</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>10.25.2.12</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>HOST00266</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>KTGE050</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>10.23.2.13</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>HOST00268</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>KTBCP053</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>10.25.2.15</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>HOST00269</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>KTBCP054</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>10.25.2.16</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>HOST00270</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>KTDB039</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>10.21.2.17</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>HOST00272</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>KTAI042</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>10.24.2.19</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>HOST00274</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>KTIPTV048</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>10.22.2.219</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>HOST00275</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>KT-GE052</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>10.23.2.22</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>HOST00276</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>KTIPTV049</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>10.22.2.23</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>HOST00277</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>KTAI043</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>10.24.2.24</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>HOST00278</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>KTIP-TV050</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>10.22.2.25</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>HOST00280</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>KTBCP055</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>10.25.2.27</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>HOST00281</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>KTBCP056</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>10.25.2.28</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>HOST00282</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>KTIPTV051</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>10.22.2.29</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>HOST00284</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>KTAI044</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>10.24.2.31</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>HOST00286</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>KTAI045</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>10.24.2.33</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>HOST00288</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>KTBCP058</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>10.25.2.35</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>HOST00289</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>KTDB041</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>10.21.2.36</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>HOST00290</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>KTBCP059</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>10.25.2.37</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>HOST00291</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>KTIPTV052</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>10.22.2.38</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>HOST00292</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>KTAI046</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>10.24.2.39</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>HOST00294</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>KTGE054</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>10.23.2.41</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>HOST00295</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>KTBCP060</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>10.25.2.42</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>HOST00296</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>KTDB042</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>10.21.2.43</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>HOST00297</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>KTDB043</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>10.21.2.44</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>HOST00298</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>KTDB044</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>10.21.2.45</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>HOST00299</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>KTDB045</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>10.21.2.46</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>HOST00300</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>KTIPTV053</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>10.22.2.185</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>HOST00301</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>KTBCP061</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>10.25.2.48</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>HOST00302</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>KTGE055</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>10.23.2.49</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>HOST00303</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>KTAI047</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>10.24.2.50</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>HOST00304</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>KTGE056</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>10.23.2.51</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>HOST00305</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>KTCLD043</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>10.20.2.52</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>HOST00306</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>KTIPTV054</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>10.22.2.53</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>HOST00307</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>KTAI048</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>10.24.2.223</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>HOST00308</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>KTB-CP062</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>10.25.2.55</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>HOST00309</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>KTAI049</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>10.24.2.56</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>HOST00310</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>KTCLD044</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>10.20.2.57</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>HOST00311</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>KTDB046</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>10.21.2.58</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>HOST00312</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>KTIPTV055</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>10.22.2.59</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>HOST00313</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>KTGE057</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>10.23.2.60</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>HOST00314</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>KTBCP063</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>10.25.2.61</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>HOST00315</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>KTGE058</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>10.23.2.62</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>HOST00316</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>KTBCP064</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>10.25.2.63</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>HOST00317</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>KTIPTV056</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>10.22.2.64</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>HOST00318</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>KTGE059</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>10.23.2.65</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>HOST00320</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>KTAI050</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>10.24.2.67</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>HOST00321</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>KTBCP065</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>10.25.2.68</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>HOST00322</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>KTAI051</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>10.24.2.69</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>HOST00323</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>KTC-LD045</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>10.20.2.70</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>HOST00324</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>KTDB047</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>10.21.2.71</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>HOST00325</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>KTBCP066</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>10.25.2.72</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>HOST00328</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>KT-AI052</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>10.24.2.75</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>HOST00331</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>KTBCP067</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>10.25.2.78</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>HOST00332</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>KTGE063</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>10.23.2.79</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>HOST00334</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>KTGE064</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>10.23.2.81</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>HOST00335</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>KTCLD047</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>10.20.2.82</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>HOST00336</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>KTAI053</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>10.24.2.83</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>HOST00341</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>KTAI054</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>10.24.2.88</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>HOST00342</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>KTCLD048</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>10.20.2.89</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>HOST00343</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>KTAI055</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>10.24.2.90</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>HOST00344</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>KTDB050</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>10.21.2.91</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>HOST00347</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>KTC-LD049</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>10.20.2.94</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>HOST00348</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>KTIPTV060</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>10.22.2.95</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>HOST00349</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>KTIPTV061</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>10.22.2.96</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>HOST00350</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>KTDB052</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>10.21.2.97</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>HOST00351</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>KTIPTV062</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>10.22.2.98</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>HOST00352</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>KTAI057</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>10.24.2.99</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>HOST00353</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>KTBCP068</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>10.25.2.168</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>HOST00355</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>KTAI059</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>10.24.2.102</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>HOST00356</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>KTDB053</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>10.21.2.103</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>HOST00357</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>KTGE066</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>10.23.2.104</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>HOST00358</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>KTGE067</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>10.23.2.105</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>HOST00359</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>KTDB054</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>10.21.2.106</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>HOST00360</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>KTCLD050</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>10.20.2.107</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>HOST00361</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>KTIPTV063</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>10.22.2.108</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>HOST00362</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>KTAI060</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>10.24.2.109</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>HOST00363</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>KTAI061</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>10.24.2.110</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>HOST00364</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>KTCLD051</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>10.20.2.111</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>HOST00365</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>KTIPTV064</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>10.22.2.162</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>HOST00366</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>KTDB055</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>10.21.2.113</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>HOST00367</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>KTBCP069</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>10.25.2.114</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>HOST00368</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>KTDB056</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>10.21.2.115</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>HOST00370</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>KTIPTV065</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>10.22.2.117</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>HOST00372</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>KTBCP070</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>10.25.2.177</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>HOST00373</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>KTCLD053</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>10.20.2.120</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>HOST00375</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>KTAI062</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>10.24.2.122</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>HOST00376</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>KTBCP071</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>10.25.2.123</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>HOST00377</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>KTDB058</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>10.21.2.124</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>HOST00378</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>KTIPTV066</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>10.22.2.125</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>HOST00379</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>KTIPTV067</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>10.22.2.78</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>HOST00380</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>KTAI063</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>10.24.2.127</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>HOST00381</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>KTIPTV068</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>10.22.2.128</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>HOST00382</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>KTAI064</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>10.24.2.129</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>HOST00383</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>KTAI065</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>10.24.2.130</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>HOST00384</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>KTIPTV069</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>10.22.2.131</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>HOST00385</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>KTCLD054</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>10.20.2.132</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>HOST00386</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>KTBCP072</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>10.25.2.133</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>HOST00387</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>KTDB059</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>10.21.2.134</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>HOST00388</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>KTGE069</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>10.23.2.135</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>HOST00389</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>KTCLD055</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>10.20.2.88</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>HOST00391</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>KTBCP073</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>10.25.2.138</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>HOST00392</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>KTDB060</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>10.21.2.139</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>HOST00393</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>KTCLD056</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>10.20.2.140</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>HOST00394</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>KTIPTV070</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>10.22.2.141</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>HOST00395</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>KTBCP074</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>10.25.2.142</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>HOST00396</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>KTBCP075</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>10.25.2.143</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>HOST00397</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>KTGE071</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>10.23.2.144</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>HOST00399</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>KTDB061</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>10.21.2.146</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>HOST00400</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>KTBCP076</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>10.25.2.147</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>HOST00401</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>KTGE073</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>10.23.2.241</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>HOST00402</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>KTCLD057</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>10.20.2.149</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>HOST00403</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>KTIP-TV071</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>10.22.2.150</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>HOST00404</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>KTB-CP077</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>10.25.2.151</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>HOST00405</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>KTAI066</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>10.24.2.152</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>HOST00406</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>KTGE074</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>10.23.2.153</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>HOST00407</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>KTGE075</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>10.23.2.154</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>HOST00409</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>KTGE076</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>10.23.2.156</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>HOST00410</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>KTBCP078</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>10.25.2.157</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>HOST00411</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>KTGE077</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>10.23.2.89</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>HOST00412</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>KTDB062</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>10.21.2.159</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>HOST00413</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>KTGE078</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>10.23.2.160</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>HOST00414</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>KTDB063</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>10.21.2.161</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>HOST00415</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>KTCLD059</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>10.20.2.162</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>HOST00416</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>KTDB064</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>10.21.2.163</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>HOST00417</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>KTAI067</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>10.24.2.164</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>HOST00418</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>KTDB065</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>10.21.2.165</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>HOST00420</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>KTAI068</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>10.24.2.167</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>HOST00421</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>KTAI069</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>10.24.2.168</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>HOST00422</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>KTIPTV073</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>10.22.2.169</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>HOST00425</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>KTCLD060</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>10.20.2.172</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>HOST00427</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>KTB-CP079</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>10.25.2.174</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>HOST00428</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>KTCLD061</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>10.20.2.175</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>HOST00429</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>KTBCP080</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>10.25.2.176</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>HOST00430</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>KTDB069</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>10.21.2.177</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>HOST00431</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>KTGE079</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>10.23.2.178</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>HOST00432</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>KTCLD062</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>10.20.2.179</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>HOST00433</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>KTGE080</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>10.23.2.180</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>HOST00434</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>KTAI070</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>10.24.2.181</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>HOST00435</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>KTBCP081</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>10.25.2.182</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>HOST00436</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>KTGE081</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>10.23.2.183</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>HOST00437</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>KTDB070</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>10.21.2.184</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>HOST00438</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>KTIPTV074</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>10.22.2.185</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>HOST00439</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>KTBCP082</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>10.25.2.186</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>HOST00440</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>KTAI071</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>10.24.2.187</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>HOST00441</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>KTCLD063</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>10.20.2.188</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>HOST00442</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>KTIP-TV075</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>10.22.2.189</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>HOST00443</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>KTIPTV076</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>10.22.2.190</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>HOST00444</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>KTAI072</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>10.24.2.191</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>HOST00445</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>KTGE082</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>10.23.2.192</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>HOST00446</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>KTIPTV077</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>10.22.2.193</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>HOST00447</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>KTB-CP083</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>10.25.2.194</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>HOST00448</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>KTDB071</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>10.21.2.195</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>HOST00450</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>KTBCP084</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>10.25.2.197</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>HOST00451</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>KTIPTV078</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>10.22.2.198</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>HOST00452</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>KTBCP085</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>10.25.2.199</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>HOST00453</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>KTBCP086</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>10.25.2.200</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>HOST00454</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>KTGE083</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>10.23.2.201</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>HOST00455</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>KTIPTV079</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>10.22.2.202</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>HOST00456</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>KTBCP087</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>10.25.2.203</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>HOST00459</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>KTDB074</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>10.21.2.206</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>HOST00460</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>KTIPTV080</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>10.22.2.207</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>HOST00461</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>KTAI073</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>10.24.2.58</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>HOST00462</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>KTAI074</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>10.24.2.209</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>HOST00463</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>KTAI075</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>10.24.2.210</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>HOST00464</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>KTBCP088</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>10.25.2.211</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2024-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>HOST00465</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>KTIPTV081</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>10.22.2.212</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>HOST00466</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>KTIPTV082</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>10.22.2.213</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>HOST00468</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>KTCLD065</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>10.20.2.211</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>HOST00469</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>KTBCP089</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>10.25.2.216</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>HOST00471</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>KTAI076</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>10.24.2.218</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>HOST00472</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>KTGE085</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>10.23.2.219</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>HOST00473</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>KTBCP090</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>10.25.2.220</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>HOST00474</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>KT-DB075</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>10.21.2.221</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2024-01-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>HOST00475</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>KTDB076</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>10.21.2.222</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>HOST00476</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>KTAI077</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>10.24.2.223</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>HOST00477</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>KTGE086</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>10.23.2.21</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>HOST00478</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>KTDB077</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>10.21.2.225</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>HOST00480</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>KTBCP091</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>10.25.2.227</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>HOST00481</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>KTDB078</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>10.21.2.228</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>HOST00482</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>KTGE087</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>10.23.2.229</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>HOST00483</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>KTDB079</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>10.21.2.230</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>HOST00484</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>KTDB080</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>10.21.2.231</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>HOST00485</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>KTIPTV083</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>10.22.2.232</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>HOST00486</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>KTDB081</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>10.21.2.233</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>HOST00487</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>KTBCP092</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>10.25.2.234</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>HOST00488</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>KTDB082</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>10.21.2.235</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>HOST00489</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>KTCLD067</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>10.20.2.236</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>HOST00490</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>KTGE088</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>10.23.2.237</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>HOST00492</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>KTIPTV085</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>10.22.2.239</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>HOST00493</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>KTIPTV086</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>10.22.2.240</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>HOST00494</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>KTDB083</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>10.21.2.241</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>HOST00495</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>KTBCP093</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>10.25.2.242</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>HOST00496</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>KTDB084</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>10.21.2.243</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>HOST00497</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>KTBCP094</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>10.25.2.244</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>HOST00499</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>KTBCP096</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>10.25.2.246</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>HOST00500</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>KTGE089</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>10.23.2.247</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>